--- a/oec-ascend/oec/test_cases/cann/base_report.xlsx
+++ b/oec-ascend/oec/test_cases/cann/base_report.xlsx
@@ -4,7 +4,7 @@
   <fileVersion appName="xl" lastEdited="3" lowestEdited="5" rupBuild="9302"/>
   <workbookPr/>
   <bookViews>
-    <workbookView windowWidth="25068" windowHeight="12900"/>
+    <workbookView windowWidth="29868" windowHeight="13500"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -28,7 +28,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="51" uniqueCount="48">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="53" uniqueCount="50">
   <si>
     <t>兼容性工具测试报告</t>
   </si>
@@ -115,6 +115,12 @@
   </si>
   <si>
     <t>图像处理、视频编解码测试</t>
+  </si>
+  <si>
+    <t>开发工具</t>
+  </si>
+  <si>
+    <t>常用开发工具基本功能验证</t>
   </si>
   <si>
     <t>算子</t>
@@ -555,7 +561,7 @@
       </patternFill>
     </fill>
   </fills>
-  <borders count="13">
+  <borders count="14">
     <border>
       <left/>
       <right/>
@@ -615,6 +621,19 @@
       </right>
       <top/>
       <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color rgb="FF000000"/>
+      </left>
+      <right style="thin">
+        <color rgb="FF000000"/>
+      </right>
+      <top/>
+      <bottom style="thin">
+        <color rgb="FF000000"/>
+      </bottom>
       <diagonal/>
     </border>
     <border>
@@ -739,7 +758,7 @@
     <xf numFmtId="0" fontId="5" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="3" borderId="5" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="0" fillId="3" borderId="6" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="6" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
@@ -751,34 +770,34 @@
     <xf numFmtId="0" fontId="8" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="6" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="6" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="7" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="7" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="7" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="8" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="11" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="12" fillId="4" borderId="8" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="5" borderId="9" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="14" fillId="5" borderId="8" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="15" fillId="6" borderId="10" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="16" fillId="0" borderId="11" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="17" fillId="0" borderId="12" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="12" fillId="4" borderId="9" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="5" borderId="10" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="5" borderId="9" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="6" borderId="11" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="16" fillId="0" borderId="12" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="17" fillId="0" borderId="13" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="18" fillId="7" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
@@ -863,7 +882,7 @@
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="21">
+  <cellXfs count="24">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
@@ -915,6 +934,15 @@
       <alignment horizontal="left"/>
     </xf>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
@@ -1271,7 +1299,7 @@
   <sheetPr>
     <outlinePr summaryBelow="0"/>
   </sheetPr>
-  <dimension ref="A1:E23"/>
+  <dimension ref="A1:E24"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="14.4" outlineLevelCol="4"/>
   <cols>
     <col min="1" max="1" width="16.7222222222222" style="3" customWidth="1"/>
@@ -1426,7 +1454,7 @@
       <c r="E14" s="7"/>
     </row>
     <row r="15" ht="21" customHeight="1" spans="1:5">
-      <c r="A15" s="19"/>
+      <c r="A15" s="20"/>
       <c r="B15" s="7" t="s">
         <v>25</v>
       </c>
@@ -1437,7 +1465,7 @@
       <c r="E15" s="7"/>
     </row>
     <row r="16" ht="21" customHeight="1" spans="1:5">
-      <c r="A16" s="19"/>
+      <c r="A16" s="20"/>
       <c r="B16" s="7" t="s">
         <v>27</v>
       </c>
@@ -1448,20 +1476,20 @@
       <c r="E16" s="7"/>
     </row>
     <row r="17" ht="19.5" customHeight="1" spans="1:5">
-      <c r="A17" s="19" t="s">
+      <c r="A17" s="21"/>
+      <c r="B17" s="15" t="s">
         <v>29</v>
       </c>
-      <c r="B17" s="15" t="s">
+      <c r="C17" s="15" t="s">
         <v>30</v>
-      </c>
-      <c r="C17" s="15" t="s">
-        <v>31</v>
       </c>
       <c r="D17" s="7"/>
       <c r="E17" s="7"/>
     </row>
     <row r="18" ht="19.5" customHeight="1" spans="1:5">
-      <c r="A18" s="19"/>
+      <c r="A18" s="22" t="s">
+        <v>31</v>
+      </c>
       <c r="B18" s="15" t="s">
         <v>32</v>
       </c>
@@ -1471,21 +1499,21 @@
       <c r="D18" s="7"/>
       <c r="E18" s="7"/>
     </row>
-    <row r="19" ht="21" customHeight="1" spans="1:5">
-      <c r="A19" s="19" t="s">
+    <row r="19" ht="19.5" customHeight="1" spans="1:5">
+      <c r="A19" s="22"/>
+      <c r="B19" s="15" t="s">
         <v>34</v>
       </c>
-      <c r="B19" s="7" t="s">
+      <c r="C19" s="15" t="s">
         <v>35</v>
-      </c>
-      <c r="C19" s="15" t="s">
-        <v>36</v>
       </c>
       <c r="D19" s="7"/>
       <c r="E19" s="7"/>
     </row>
     <row r="20" ht="21" customHeight="1" spans="1:5">
-      <c r="A20" s="19"/>
+      <c r="A20" s="22" t="s">
+        <v>36</v>
+      </c>
       <c r="B20" s="7" t="s">
         <v>37</v>
       </c>
@@ -1495,8 +1523,8 @@
       <c r="D20" s="7"/>
       <c r="E20" s="7"/>
     </row>
-    <row r="21" ht="24" customHeight="1" spans="1:5">
-      <c r="A21" s="19"/>
+    <row r="21" ht="21" customHeight="1" spans="1:5">
+      <c r="A21" s="22"/>
       <c r="B21" s="7" t="s">
         <v>39</v>
       </c>
@@ -1507,20 +1535,20 @@
       <c r="E21" s="7"/>
     </row>
     <row r="22" ht="24" customHeight="1" spans="1:5">
-      <c r="A22" s="20" t="s">
+      <c r="A22" s="22"/>
+      <c r="B22" s="7" t="s">
         <v>41</v>
       </c>
-      <c r="B22" s="7" t="s">
+      <c r="C22" s="15" t="s">
         <v>42</v>
-      </c>
-      <c r="C22" s="15" t="s">
-        <v>43</v>
       </c>
       <c r="D22" s="7"/>
       <c r="E22" s="7"/>
     </row>
     <row r="23" ht="24" customHeight="1" spans="1:5">
-      <c r="A23" s="19"/>
+      <c r="A23" s="23" t="s">
+        <v>43</v>
+      </c>
       <c r="B23" s="7" t="s">
         <v>44</v>
       </c>
@@ -1529,16 +1557,27 @@
       </c>
       <c r="D23" s="7"/>
       <c r="E23" s="7"/>
+    </row>
+    <row r="24" ht="24" customHeight="1" spans="1:5">
+      <c r="A24" s="22"/>
+      <c r="B24" s="7" t="s">
+        <v>46</v>
+      </c>
+      <c r="C24" s="15" t="s">
+        <v>47</v>
+      </c>
+      <c r="D24" s="7"/>
+      <c r="E24" s="7"/>
     </row>
   </sheetData>
   <mergeCells count="8">
     <mergeCell ref="A1:E1"/>
     <mergeCell ref="A2:C2"/>
     <mergeCell ref="A10:A13"/>
-    <mergeCell ref="A14:A16"/>
-    <mergeCell ref="A17:A18"/>
-    <mergeCell ref="A19:A21"/>
-    <mergeCell ref="A22:A23"/>
+    <mergeCell ref="A14:A17"/>
+    <mergeCell ref="A18:A19"/>
+    <mergeCell ref="A20:A22"/>
+    <mergeCell ref="A23:A24"/>
     <mergeCell ref="A3:C6"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
@@ -1569,10 +1608,10 @@
         <v>9</v>
       </c>
       <c r="C1" s="2" t="s">
-        <v>46</v>
+        <v>48</v>
       </c>
       <c r="D1" s="2" t="s">
-        <v>47</v>
+        <v>49</v>
       </c>
       <c r="E1" s="2" t="s">
         <v>12</v>
